--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7553,6 +7553,27 @@
       <c r="E339" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>339.14</v>
+      </c>
+      <c r="C340" t="n">
+        <v>314.62</v>
+      </c>
+      <c r="D340" t="n">
+        <v>323.63</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11090,6 +11111,16 @@
       </c>
       <c r="B352" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -11258,28 +11289,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2085636232595801</v>
+        <v>0.2056614843709234</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1016429228779627</v>
+        <v>0.09936158163625719</v>
       </c>
       <c r="M2" t="n">
-        <v>3.749253812594771</v>
+        <v>3.752736505703626</v>
       </c>
       <c r="N2" t="n">
-        <v>20.71979331934492</v>
+        <v>20.73095174152885</v>
       </c>
       <c r="O2" t="n">
-        <v>4.551899968073213</v>
+        <v>4.553125491519957</v>
       </c>
       <c r="P2" t="n">
-        <v>338.6266105104861</v>
+        <v>338.6571730602283</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11336,28 +11367,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1968047722489407</v>
+        <v>0.1925130140381082</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08253488647195373</v>
+        <v>0.07921810484292191</v>
       </c>
       <c r="M3" t="n">
-        <v>3.876240501428107</v>
+        <v>3.887795904286762</v>
       </c>
       <c r="N3" t="n">
-        <v>23.20383114366983</v>
+        <v>23.29345156320164</v>
       </c>
       <c r="O3" t="n">
-        <v>4.817035514055282</v>
+        <v>4.826328994505207</v>
       </c>
       <c r="P3" t="n">
-        <v>316.8053765319996</v>
+        <v>316.8505732227276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11414,28 +11445,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06367463052617126</v>
+        <v>0.06346313113177812</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009959408314573981</v>
+        <v>0.009955556521248243</v>
       </c>
       <c r="M4" t="n">
-        <v>3.828430050539994</v>
+        <v>3.818311724999545</v>
       </c>
       <c r="N4" t="n">
-        <v>21.72144811804495</v>
+        <v>21.65775692724846</v>
       </c>
       <c r="O4" t="n">
-        <v>4.660627438236718</v>
+        <v>4.653789523307695</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3228274428604</v>
+        <v>322.3250547521001</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11473,7 +11504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20629,6 +20660,33 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-35.46295537104788,174.4359610959785</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-35.46345435040396,174.43667545277205</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-35.46367583874941,174.43753630976002</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7572,6 +7572,27 @@
         <v>323.63</v>
       </c>
       <c r="E340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="C341" t="n">
+        <v>313.82</v>
+      </c>
+      <c r="D341" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="E341" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7588,7 +7609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11121,6 +11142,16 @@
       </c>
       <c r="B353" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -11289,28 +11320,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2056614843709234</v>
+        <v>0.201905146793115</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09936158163625719</v>
+        <v>0.09615165842744322</v>
       </c>
       <c r="M2" t="n">
-        <v>3.752736505703626</v>
+        <v>3.760349202625273</v>
       </c>
       <c r="N2" t="n">
-        <v>20.73095174152885</v>
+        <v>20.79097378969571</v>
       </c>
       <c r="O2" t="n">
-        <v>4.553125491519957</v>
+        <v>4.559712029250938</v>
       </c>
       <c r="P2" t="n">
-        <v>338.6571730602283</v>
+        <v>338.6968854493568</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11367,28 +11398,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1925130140381082</v>
+        <v>0.1877845124353714</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07921810484292191</v>
+        <v>0.07553144853152027</v>
       </c>
       <c r="M3" t="n">
-        <v>3.887795904286762</v>
+        <v>3.902075103360875</v>
       </c>
       <c r="N3" t="n">
-        <v>23.29345156320164</v>
+        <v>23.41666998410779</v>
       </c>
       <c r="O3" t="n">
-        <v>4.826328994505207</v>
+        <v>4.839077389762204</v>
       </c>
       <c r="P3" t="n">
-        <v>316.8505732227276</v>
+        <v>316.9005634304106</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11445,28 +11476,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06346313113177812</v>
+        <v>0.06337123506913392</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009955556521248243</v>
+        <v>0.009989179941209181</v>
       </c>
       <c r="M4" t="n">
-        <v>3.818311724999545</v>
+        <v>3.807586514177218</v>
       </c>
       <c r="N4" t="n">
-        <v>21.65775692724846</v>
+        <v>21.59413005800719</v>
       </c>
       <c r="O4" t="n">
-        <v>4.653789523307695</v>
+        <v>4.646948467328553</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3250547521001</v>
+        <v>322.3260262867728</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11504,7 +11535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20687,6 +20718,33 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-35.46296778484203,174.43595454212252</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-35.46346097110508,174.43667195739775</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-35.46367410081145,174.43753722728553</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7595,6 +7595,27 @@
       <c r="E341" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>334.92</v>
+      </c>
+      <c r="C342" t="n">
+        <v>312.78</v>
+      </c>
+      <c r="D342" t="n">
+        <v>325.51</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11152,6 +11173,16 @@
       </c>
       <c r="B354" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -11320,28 +11351,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.201905146793115</v>
+        <v>0.196448457054659</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09615165842744322</v>
+        <v>0.09107092412454498</v>
       </c>
       <c r="M2" t="n">
-        <v>3.760349202625273</v>
+        <v>3.77585985486431</v>
       </c>
       <c r="N2" t="n">
-        <v>20.79097378969571</v>
+        <v>20.97426199867746</v>
       </c>
       <c r="O2" t="n">
-        <v>4.559712029250938</v>
+        <v>4.579766587794345</v>
       </c>
       <c r="P2" t="n">
-        <v>338.6968854493568</v>
+        <v>338.7553903217384</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11398,28 +11429,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1877845124353714</v>
+        <v>0.1823491469766348</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07553144853152027</v>
+        <v>0.07128447148427519</v>
       </c>
       <c r="M3" t="n">
-        <v>3.902075103360875</v>
+        <v>3.919829745831171</v>
       </c>
       <c r="N3" t="n">
-        <v>23.41666998410779</v>
+        <v>23.59035284920915</v>
       </c>
       <c r="O3" t="n">
-        <v>4.839077389762204</v>
+        <v>4.856990101823262</v>
       </c>
       <c r="P3" t="n">
-        <v>316.9005634304106</v>
+        <v>316.9588396707235</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11476,28 +11507,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06337123506913392</v>
+        <v>0.06426201831331824</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009989179941209181</v>
+        <v>0.01033344845754558</v>
       </c>
       <c r="M4" t="n">
-        <v>3.807586514177218</v>
+        <v>3.800372704997448</v>
       </c>
       <c r="N4" t="n">
-        <v>21.59413005800719</v>
+        <v>21.53731348588807</v>
       </c>
       <c r="O4" t="n">
-        <v>4.646948467328553</v>
+        <v>4.640831120164584</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3260262867728</v>
+        <v>322.3164755953246</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11535,7 +11566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20745,6 +20776,33 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.46299029518784,174.43594265779203</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.463469578016394,174.43666741341033</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.463660280066506,174.4375445237965</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E342"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7616,6 +7616,48 @@
       <c r="E342" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="C343" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="D343" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="C344" t="n">
+        <v>316.54</v>
+      </c>
+      <c r="D344" t="n">
+        <v>325.81</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11183,6 +11225,26 @@
       </c>
       <c r="B355" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -11351,28 +11413,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.196448457054659</v>
+        <v>0.1902020733562883</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09107092412454498</v>
+        <v>0.08629317188394425</v>
       </c>
       <c r="M2" t="n">
-        <v>3.77585985486431</v>
+        <v>3.784078003369633</v>
       </c>
       <c r="N2" t="n">
-        <v>20.97426199867746</v>
+        <v>21.01366100621483</v>
       </c>
       <c r="O2" t="n">
-        <v>4.579766587794345</v>
+        <v>4.584065990604283</v>
       </c>
       <c r="P2" t="n">
-        <v>338.7553903217384</v>
+        <v>338.8226320232845</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11429,28 +11491,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1823491469766348</v>
+        <v>0.1764855480376395</v>
       </c>
       <c r="J3" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07128447148427519</v>
+        <v>0.06752630031852913</v>
       </c>
       <c r="M3" t="n">
-        <v>3.919829745831171</v>
+        <v>3.928253604409327</v>
       </c>
       <c r="N3" t="n">
-        <v>23.59035284920915</v>
+        <v>23.5951488744424</v>
       </c>
       <c r="O3" t="n">
-        <v>4.856990101823262</v>
+        <v>4.857483800739062</v>
       </c>
       <c r="P3" t="n">
-        <v>316.9588396707235</v>
+        <v>317.0219646813484</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11507,28 +11569,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06426201831331824</v>
+        <v>0.06460214021342313</v>
       </c>
       <c r="J4" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01033344845754558</v>
+        <v>0.01057300798585425</v>
       </c>
       <c r="M4" t="n">
-        <v>3.800372704997448</v>
+        <v>3.786668520069285</v>
       </c>
       <c r="N4" t="n">
-        <v>21.53731348588807</v>
+        <v>21.42494897969331</v>
       </c>
       <c r="O4" t="n">
-        <v>4.640831120164584</v>
+        <v>4.628709213127706</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3164755953246</v>
+        <v>322.3128055798014</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11566,7 +11628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E342"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20803,6 +20865,60 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.46296199173812,174.4359576005889</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.463432998642205,174.43668672535037</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.46368229394747,174.4375329018078</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.4629557020824,174.43596092120904</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.463438460720894,174.4366838416681</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.4636577972979,174.43754583454674</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
